--- a/data/pupil/3_processed/15_semantic_similarity/event/sub_1012_cosine_similarity.xlsx
+++ b/data/pupil/3_processed/15_semantic_similarity/event/sub_1012_cosine_similarity.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,20 +436,30 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Pool Party</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Sea Ice</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Natalie Wood</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Grandfather Clocks</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Impatient Billionaire</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Dont Look</t>
         </is>
@@ -460,15 +470,21 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
         <v>0.4004336893558502</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>0.03400791436433792</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>0.2483311593532562</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
         <v>0.3011903166770935</v>
       </c>
     </row>
@@ -477,15 +493,21 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
         <v>0.6800457835197449</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>0.08315423130989075</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>0.3010095059871674</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
         <v>0.2495452165603638</v>
       </c>
     </row>
@@ -494,15 +516,21 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
         <v>0.5877675414085388</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>0.6504856944084167</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>0.2735673785209656</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
         <v>0.3867799639701843</v>
       </c>
     </row>
@@ -511,15 +539,21 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
         <v>0.5049666166305542</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>0.5719738602638245</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>0.5124802589416504</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
         <v>0.3890345394611359</v>
       </c>
     </row>
@@ -531,12 +565,18 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
         <v>0.4492656290531158</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>0.2006449401378632</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
         <v>0.4370797574520111</v>
       </c>
     </row>
@@ -545,15 +585,21 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
         <v>0.4054703116416931</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>0.3851140439510345</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>0.7118850350379944</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
         <v>0.4492690861225128</v>
       </c>
     </row>
@@ -562,15 +608,21 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
         <v>0.3520370721817017</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>0.329590380191803</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>0.4219197928905487</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
         <v>0.4298296868801117</v>
       </c>
     </row>
@@ -585,9 +637,15 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
         <v>0.6788411736488342</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -596,15 +654,21 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
         <v>0.2212672233581543</v>
       </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
       <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
         <v>0.618969202041626</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -619,9 +683,15 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
         <v>0.3862919807434082</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
         <v>0.1483582109212875</v>
       </c>
     </row>
@@ -639,6 +709,12 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
         <v>0.1334993988275528</v>
       </c>
     </row>
@@ -647,15 +723,21 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" t="n">
         <v>0.5418553352355957</v>
       </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
       <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
         <v>0.604293167591095</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
         <v>0.1090441644191742</v>
       </c>
     </row>
@@ -664,15 +746,21 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" t="n">
         <v>0.5874042510986328</v>
       </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
       <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
         <v>0.5813530087471008</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
         <v>0.1613299697637558</v>
       </c>
     </row>
@@ -690,6 +778,12 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
         <v>0.4437059164047241</v>
       </c>
     </row>
@@ -698,15 +792,21 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="n">
         <v>0.6583863496780396</v>
       </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
         <v>0.513222336769104</v>
       </c>
     </row>
@@ -715,15 +815,21 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" t="n">
         <v>0.5786846876144409</v>
       </c>
-      <c r="C17" t="n">
+      <c r="D17" t="n">
         <v>0.4651632010936737</v>
       </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
       <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
         <v>0.588815450668335</v>
       </c>
     </row>
@@ -735,12 +841,18 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
         <v>0.1369621902704239</v>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
         <v>0.5630795359611511</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
         <v>0.5328367948532104</v>
       </c>
     </row>
@@ -752,12 +864,16 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
         <v>0.2873531579971313</v>
       </c>
-      <c r="D19" t="n">
+      <c r="E19" t="n">
         <v>0.5099642276763916</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -772,9 +888,13 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
         <v>0.4910346865653992</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -783,15 +903,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" t="n">
         <v>0.4797606468200684</v>
       </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -799,9 +923,7 @@
       <c r="A22" t="n">
         <v>21</v>
       </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
+      <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
         <v>0</v>
       </c>
@@ -809,6 +931,10 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -816,16 +942,18 @@
       <c r="A23" t="n">
         <v>22</v>
       </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
+      <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
         <v>0.4529750645160675</v>
       </c>
-      <c r="D23" t="n">
+      <c r="E23" t="n">
         <v>0.2877053618431091</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -833,16 +961,18 @@
       <c r="A24" t="n">
         <v>23</v>
       </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
         <v>0.7893776893615723</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -851,13 +981,15 @@
         <v>24</v>
       </c>
       <c r="B25" t="inlineStr"/>
-      <c r="C25" t="n">
-        <v>0</v>
-      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
         <v>0.6943458318710327</v>
       </c>
-      <c r="E25" t="n">
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -866,13 +998,15 @@
         <v>25</v>
       </c>
       <c r="B26" t="inlineStr"/>
-      <c r="C26" t="n">
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="n">
         <v>0.4791254997253418</v>
       </c>
-      <c r="D26" t="n">
+      <c r="E26" t="n">
         <v>0.4829646944999695</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -881,13 +1015,15 @@
         <v>26</v>
       </c>
       <c r="B27" t="inlineStr"/>
-      <c r="C27" t="n">
-        <v>0</v>
-      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
         <v>0.3316630125045776</v>
       </c>
-      <c r="E27" t="n">
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -896,13 +1032,15 @@
         <v>27</v>
       </c>
       <c r="B28" t="inlineStr"/>
-      <c r="C28" t="n">
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="n">
         <v>0.4885505139827728</v>
       </c>
-      <c r="D28" t="n">
+      <c r="E28" t="n">
         <v>0.3250418305397034</v>
       </c>
-      <c r="E28" t="n">
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -911,13 +1049,15 @@
         <v>28</v>
       </c>
       <c r="B29" t="inlineStr"/>
-      <c r="C29" t="n">
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="n">
         <v>0.631246030330658</v>
       </c>
-      <c r="D29" t="n">
+      <c r="E29" t="n">
         <v>0.2350159287452698</v>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -926,13 +1066,15 @@
         <v>29</v>
       </c>
       <c r="B30" t="inlineStr"/>
-      <c r="C30" t="n">
-        <v>0</v>
-      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
         <v>0.3649097681045532</v>
       </c>
-      <c r="E30" t="n">
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="n">
         <v>0.4827630519866943</v>
       </c>
     </row>
@@ -941,11 +1083,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="inlineStr"/>
-      <c r="C31" t="n">
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="n">
         <v>0.1470921635627747</v>
       </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="n">
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="n">
         <v>0.4987107217311859</v>
       </c>
     </row>
@@ -954,11 +1098,13 @@
         <v>31</v>
       </c>
       <c r="B32" t="inlineStr"/>
-      <c r="C32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="n">
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -967,11 +1113,13 @@
         <v>32</v>
       </c>
       <c r="B33" t="inlineStr"/>
-      <c r="C33" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="n">
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="n">
         <v>0.7976973056793213</v>
       </c>
     </row>
@@ -980,11 +1128,13 @@
         <v>33</v>
       </c>
       <c r="B34" t="inlineStr"/>
-      <c r="C34" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="n">
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="n">
         <v>0.7397394180297852</v>
       </c>
     </row>
@@ -993,11 +1143,13 @@
         <v>34</v>
       </c>
       <c r="B35" t="inlineStr"/>
-      <c r="C35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="n">
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="n">
         <v>0.7417396306991577</v>
       </c>
     </row>
@@ -1006,11 +1158,13 @@
         <v>35</v>
       </c>
       <c r="B36" t="inlineStr"/>
-      <c r="C36" t="n">
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="n">
         <v>0.3009501397609711</v>
       </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="n">
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="n">
         <v>0.4225446581840515</v>
       </c>
     </row>
@@ -1019,11 +1173,13 @@
         <v>36</v>
       </c>
       <c r="B37" t="inlineStr"/>
-      <c r="C37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="n">
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1032,11 +1188,13 @@
         <v>37</v>
       </c>
       <c r="B38" t="inlineStr"/>
-      <c r="C38" t="n">
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="n">
         <v>0.6244675517082214</v>
       </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="n">
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1045,11 +1203,13 @@
         <v>38</v>
       </c>
       <c r="B39" t="inlineStr"/>
-      <c r="C39" t="n">
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="n">
         <v>0.4723442196846008</v>
       </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="n">
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1058,11 +1218,13 @@
         <v>39</v>
       </c>
       <c r="B40" t="inlineStr"/>
-      <c r="C40" t="n">
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="n">
         <v>0.2425564527511597</v>
       </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="n">
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1071,11 +1233,13 @@
         <v>40</v>
       </c>
       <c r="B41" t="inlineStr"/>
-      <c r="C41" t="n">
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="n">
         <v>0.3393508493900299</v>
       </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="n">
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1084,11 +1248,13 @@
         <v>41</v>
       </c>
       <c r="B42" t="inlineStr"/>
-      <c r="C42" t="n">
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="n">
         <v>0.2235362529754639</v>
       </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="n">
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1097,154 +1263,182 @@
         <v>42</v>
       </c>
       <c r="B43" t="inlineStr"/>
-      <c r="C43" t="n">
-        <v>0</v>
-      </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
       <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
         <v>43</v>
       </c>
       <c r="B44" t="inlineStr"/>
-      <c r="C44" t="n">
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="n">
         <v>0.4551621675491333</v>
       </c>
-      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
         <v>44</v>
       </c>
       <c r="B45" t="inlineStr"/>
-      <c r="C45" t="n">
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="n">
         <v>0.3608128428459167</v>
       </c>
-      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
         <v>45</v>
       </c>
       <c r="B46" t="inlineStr"/>
-      <c r="C46" t="n">
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="n">
         <v>0.08218985795974731</v>
       </c>
-      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
         <v>46</v>
       </c>
       <c r="B47" t="inlineStr"/>
-      <c r="C47" t="n">
-        <v>0</v>
-      </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
       <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
         <v>47</v>
       </c>
       <c r="B48" t="inlineStr"/>
-      <c r="C48" t="n">
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="n">
         <v>0.4424844682216644</v>
       </c>
-      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
         <v>48</v>
       </c>
       <c r="B49" t="inlineStr"/>
-      <c r="C49" t="n">
-        <v>0</v>
-      </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
       <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
         <v>49</v>
       </c>
       <c r="B50" t="inlineStr"/>
-      <c r="C50" t="n">
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="n">
         <v>0.4240695834159851</v>
       </c>
-      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
         <v>50</v>
       </c>
       <c r="B51" t="inlineStr"/>
-      <c r="C51" t="n">
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="n">
         <v>0.4097154140472412</v>
       </c>
-      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
         <v>51</v>
       </c>
       <c r="B52" t="inlineStr"/>
-      <c r="C52" t="n">
-        <v>0</v>
-      </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
       <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
         <v>52</v>
       </c>
       <c r="B53" t="inlineStr"/>
-      <c r="C53" t="n">
-        <v>0</v>
-      </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
       <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
         <v>53</v>
       </c>
       <c r="B54" t="inlineStr"/>
-      <c r="C54" t="n">
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="n">
         <v>0.4605092108249664</v>
       </c>
-      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
         <v>54</v>
       </c>
       <c r="B55" t="inlineStr"/>
-      <c r="C55" t="n">
-        <v>0</v>
-      </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
       <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
         <v>55</v>
       </c>
       <c r="B56" t="inlineStr"/>
-      <c r="C56" t="n">
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="n">
         <v>0.4561439752578735</v>
       </c>
-      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
